--- a/Trading_Performance_Analytics_DashboardV1 from Chat.xlsx
+++ b/Trading_Performance_Analytics_DashboardV1 from Chat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ntuthuzelo\Downloads\Trading Journal Dashboard Project w Claude\Trading_Performance_Analytics_Project\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECAEE1E-F187-4D17-B7F3-DD3D6D35DBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A4C455-0FEA-43D8-A539-B2A84CB5C672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="20460" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_README" sheetId="1" r:id="rId1"/>
@@ -543,13 +543,13 @@
     <t>Column definitions and its analytics use.</t>
   </si>
   <si>
-    <t>Read this sheet first, then review Executive Dashboard, Performance Analytics, Behavioral Insights, Risk &amp; Strategy, Cleaned Trades, Analysis Tables&amp; Data Dictionary.</t>
-  </si>
-  <si>
     <t>I built this workbook from the available trades that I took. More journal entries from future trades will make the analytics stronger over time.</t>
   </si>
   <si>
     <t>Notion trading journal: Main Trading Journal + Atlas Funded 5K account journal.</t>
+  </si>
+  <si>
+    <t>Read this sheet first, then continue to Executive Dashboard, Performance Analytics, Behavioral Insights, Risk &amp; Strategy, Cleaned Trades, Analysis Tables&amp; Data Dictionary.</t>
   </si>
 </sst>
 </file>
@@ -10169,7 +10169,7 @@
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -10211,7 +10211,7 @@
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="23"/>
@@ -10253,7 +10253,7 @@
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
